--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.84729764541839</v>
+        <v>7.125185867380488</v>
       </c>
       <c r="D2" t="n">
-        <v>52.27351259270552</v>
+        <v>8.494445796314647</v>
       </c>
       <c r="E2" t="n">
-        <v>8.109574403721489</v>
+        <v>1.317805840604742</v>
       </c>
       <c r="F2" t="n">
-        <v>13.12005938200571</v>
+        <v>2.132009649575927</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.52709958569223</v>
+        <v>6.748153682674988</v>
       </c>
       <c r="D3" t="n">
-        <v>43.16789926734934</v>
+        <v>7.014783630944268</v>
       </c>
       <c r="E3" t="n">
-        <v>8.109574403721489</v>
+        <v>1.317805840604742</v>
       </c>
       <c r="F3" t="n">
-        <v>13.12005938200571</v>
+        <v>2.132009649575927</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.06340618658101</v>
+        <v>8.297803505319415</v>
       </c>
       <c r="D4" t="n">
-        <v>51.01583257683896</v>
+        <v>8.290072793736332</v>
       </c>
       <c r="E4" t="n">
-        <v>8.109574403721489</v>
+        <v>1.317805840604742</v>
       </c>
       <c r="F4" t="n">
-        <v>13.12005938200571</v>
+        <v>2.132009649575927</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.61632157749438</v>
+        <v>8.062652256342837</v>
       </c>
       <c r="D5" t="n">
-        <v>40.30433051069924</v>
+        <v>6.549453707988627</v>
       </c>
       <c r="E5" t="n">
-        <v>8.109574403721489</v>
+        <v>1.317805840604742</v>
       </c>
       <c r="F5" t="n">
-        <v>13.12005938200571</v>
+        <v>2.132009649575927</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.83024648946884</v>
+        <v>8.747415054538687</v>
       </c>
       <c r="D6" t="n">
-        <v>23.73019380910208</v>
+        <v>3.856156493979089</v>
       </c>
       <c r="E6" t="n">
-        <v>8.109574403721489</v>
+        <v>1.317805840604742</v>
       </c>
       <c r="F6" t="n">
-        <v>13.12005938200571</v>
+        <v>2.132009649575927</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.5377865878953</v>
+        <v>9.349890320532987</v>
       </c>
       <c r="D7" t="n">
-        <v>21.71703917492528</v>
+        <v>3.529018865925357</v>
       </c>
       <c r="E7" t="n">
-        <v>8.109574403721489</v>
+        <v>1.317805840604742</v>
       </c>
       <c r="F7" t="n">
-        <v>13.12005938200571</v>
+        <v>2.132009649575927</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>59.87471450023617</v>
+        <v>9.729641106288378</v>
       </c>
       <c r="D8" t="n">
-        <v>21.03146452342299</v>
+        <v>3.417612985056237</v>
       </c>
       <c r="E8" t="n">
-        <v>8.109574403721489</v>
+        <v>1.317805840604742</v>
       </c>
       <c r="F8" t="n">
-        <v>13.12005938200571</v>
+        <v>2.132009649575927</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>64.49676747489066</v>
+        <v>10.48072471466973</v>
       </c>
       <c r="D9" t="n">
-        <v>26.71700359388736</v>
+        <v>4.341513084006696</v>
       </c>
       <c r="E9" t="n">
-        <v>8.109574403721489</v>
+        <v>1.317805840604742</v>
       </c>
       <c r="F9" t="n">
-        <v>13.12005938200571</v>
+        <v>2.132009649575927</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.01334541459104</v>
+        <v>6.014668629871045</v>
       </c>
       <c r="D10" t="n">
-        <v>45.12491827293987</v>
+        <v>7.332799219352728</v>
       </c>
       <c r="E10" t="n">
-        <v>8.109574403721489</v>
+        <v>1.317805840604742</v>
       </c>
       <c r="F10" t="n">
-        <v>13.12005938200571</v>
+        <v>2.132009649575927</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>53.95414182322187</v>
+        <v>8.767548046273555</v>
       </c>
       <c r="D11" t="n">
-        <v>27.70148912964789</v>
+        <v>4.501491983567782</v>
       </c>
       <c r="E11" t="n">
-        <v>8.109574403721489</v>
+        <v>1.317805840604742</v>
       </c>
       <c r="F11" t="n">
-        <v>13.12005938200571</v>
+        <v>2.132009649575927</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>44.00579530024212</v>
+        <v>7.150941736289345</v>
       </c>
       <c r="D12" t="n">
-        <v>44.28032233097723</v>
+        <v>7.195552378783801</v>
       </c>
       <c r="E12" t="n">
-        <v>8.109574403721489</v>
+        <v>1.317805840604742</v>
       </c>
       <c r="F12" t="n">
-        <v>13.12005938200571</v>
+        <v>2.132009649575927</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>60.13341648183461</v>
+        <v>9.771680178298125</v>
       </c>
       <c r="D13" t="n">
-        <v>62.10478091862461</v>
+        <v>10.0920268992765</v>
       </c>
       <c r="E13" t="n">
-        <v>8.109574403721489</v>
+        <v>1.317805840604742</v>
       </c>
       <c r="F13" t="n">
-        <v>13.12005938200571</v>
+        <v>2.132009649575927</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
